--- a/output/pdf_financials_xlsx/GGL.xlsx
+++ b/output/pdf_financials_xlsx/GGL.xlsx
@@ -6384,19 +6384,19 @@
         </is>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>4.133619</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>4.133619</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>4.181619</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>4.217619</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>4.217619</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0.124605</v>
@@ -6420,13 +6420,13 @@
         <v>0.382474</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>0.48964</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>0.506754</v>
       </c>
       <c r="R92" s="3" t="n">
-        <v>0</v>
+        <v>0.317891</v>
       </c>
     </row>
     <row r="93">
@@ -8085,25 +8085,25 @@
         </is>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0</v>
+        <v>-0.631197</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0</v>
+        <v>-0.253358</v>
       </c>
       <c r="N118" s="3" t="n">
-        <v>0</v>
+        <v>-1.02401</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0</v>
+        <v>-1.083643</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>0</v>
+        <v>-0.932778</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>0</v>
+        <v>-0.492528</v>
       </c>
       <c r="R118" s="3" t="n">
-        <v>0</v>
+        <v>-0.055755</v>
       </c>
     </row>
     <row r="119">
@@ -10567,7 +10567,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -14002,7 +14006,11 @@
           <t>Reserves 8</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -22622,7 +22630,11 @@
           <t>Share-based Payments Reserve</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -26986,7 +26998,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr"/>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E179" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GGL.xlsx
+++ b/output/pdf_financials_xlsx/GGL.xlsx
@@ -1109,19 +1109,19 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.076548</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.000744</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.00076</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001708</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.000875</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -1149,25 +1149,25 @@
         </is>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.007062</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.002956</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>0.005538</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>0.011328</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>0.012269</v>
       </c>
       <c r="Q12" s="3" t="n">
-        <v>0</v>
+        <v>0.00678</v>
       </c>
       <c r="R12" s="3" t="n">
-        <v>0</v>
+        <v>0.002702</v>
       </c>
     </row>
     <row r="13">
@@ -2209,19 +2209,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-2.733967</v>
+        <v>-2.810515</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-7.831927</v>
+        <v>-7.832671</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-2.291282</v>
+        <v>-2.292042</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-9.274333</v>
+        <v>-9.276040999999999</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-16.69071</v>
+        <v>-16.691585</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -2249,25 +2249,25 @@
         </is>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.527272</v>
+        <v>-0.534334</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-0.7251570000000001</v>
+        <v>-0.728113</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.34643</v>
+        <v>-0.351968</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-1.95612</v>
+        <v>-1.967448</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-0.437755</v>
+        <v>-0.450024</v>
       </c>
       <c r="Q27" s="3" t="n">
-        <v>-0.275949</v>
+        <v>-0.282729</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>-0.420444</v>
+        <v>-0.423146</v>
       </c>
     </row>
     <row r="28">
@@ -2345,19 +2345,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-2.733967</v>
+        <v>-2.810515</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-7.831927</v>
+        <v>-7.832671</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-2.291282</v>
+        <v>-2.292042</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-9.274333</v>
+        <v>-9.276040999999999</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-16.69071</v>
+        <v>-16.691585</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -2385,25 +2385,25 @@
         </is>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.527272</v>
+        <v>-0.534334</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.7251570000000001</v>
+        <v>-0.728113</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.342917</v>
+        <v>-0.348455</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-1.954003</v>
+        <v>-1.965331</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-0.437755</v>
+        <v>-0.450024</v>
       </c>
       <c r="Q29" s="3" t="n">
-        <v>-0.275949</v>
+        <v>-0.282729</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>-0.420444</v>
+        <v>-0.423146</v>
       </c>
     </row>
     <row r="30">
@@ -2682,19 +2682,19 @@
         </is>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.18468</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.135701</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.03867</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.07015200000000001</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.038706</v>
       </c>
       <c r="I34" s="3" t="n">
         <v>0.033591</v>
@@ -2806,19 +2806,19 @@
         </is>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.18468</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.135701</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.03867</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.07015200000000001</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.038706</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.058591</v>
@@ -3550,19 +3550,19 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.187996</v>
+        <v>0.003316</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.182399</v>
+        <v>0.046698</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.875775</v>
+        <v>3.837105</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>2.392836</v>
+        <v>2.322684</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>2.310323</v>
+        <v>2.271617</v>
       </c>
       <c r="I48" s="3" t="n">
         <v>2.058469</v>
@@ -16406,7 +16406,11 @@
           <t>Reclamation deposits 7</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -23895,7 +23899,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -24311,7 +24315,7 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -26018,7 +26022,11 @@
           <t>Loss on transfer of reclamation deposit 6</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -29255,7 +29263,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -38003,7 +38015,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E290" t="inlineStr">
@@ -43559,7 +43571,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E346" t="inlineStr">
@@ -43662,7 +43674,7 @@
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E347" t="inlineStr">
@@ -46761,7 +46773,7 @@
       </c>
       <c r="D378" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E378" s="5" t="n">
@@ -47159,7 +47171,7 @@
       </c>
       <c r="D382" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E382" s="5" t="n">

--- a/output/pdf_financials_xlsx/GGL.xlsx
+++ b/output/pdf_financials_xlsx/GGL.xlsx
@@ -7640,10 +7640,10 @@
         <v>0</v>
       </c>
       <c r="C112" s="3" t="n">
-        <v>0</v>
+        <v>0.4051</v>
       </c>
       <c r="D112" s="3" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="E112" s="3" t="n">
         <v>0</v>
@@ -34956,7 +34956,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D259" t="inlineStr"/>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E259" t="inlineStr">
         <is>
           <t>-</t>
